--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260714.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260714.xlsx
@@ -777,17 +777,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>387,039,816</t>
+          <t>28,736,431</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -799,17 +799,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>28,736,431</t>
+          <t>387,039,816</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,608</t>
+          <t>8,026,400</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>8,026,400</t>
+          <t>1,608</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>279,950,185</t>
+          <t>2,270,168</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>24,839,867</t>
+          <t>67,356,770</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>83,071,614</t>
+          <t>24,839,867</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>67,356,770</t>
+          <t>83,071,614</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>2,270,168</t>
+          <t>279,950,185</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>200,165,318</t>
+          <t>1,242,514</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,242,514</t>
+          <t>200,165,318</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>3,892,488</t>
+          <t>1,748,672</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,748,672</t>
+          <t>3,892,488</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
